--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -400,7 +400,7 @@
     <t>AssignedCustodian.representedCustodianOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CustodianOrganization
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CustodianOrganization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-custodian-organization}
 </t>
   </si>
 </sst>
@@ -716,7 +716,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="170.70703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1281,7 +1281,7 @@
         <v>80</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>74</v>
@@ -1382,7 +1382,7 @@
         <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1485,7 +1485,7 @@
         <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>74</v>
@@ -1893,7 +1893,7 @@
         <v>80</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,6 +311,10 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
   </si>
   <si>
     <t>AssignedCustodian.typeId.nullFlavor</t>
@@ -1257,7 +1261,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1265,10 +1269,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1366,17 +1370,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1394,11 +1398,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1449,7 +1453,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1469,17 +1473,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1497,11 +1501,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1552,7 +1556,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1572,17 +1576,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1600,11 +1604,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1613,7 +1617,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1655,7 +1659,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1675,17 +1679,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1703,11 +1707,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1758,7 +1762,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1778,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1808,7 +1812,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1859,7 +1863,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -1879,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1916,7 +1920,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -1938,7 +1942,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -1956,7 +1960,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -1976,10 +1980,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2002,7 +2006,7 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -2055,7 +2059,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="129">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -406,6 +406,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CustodianOrganization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-custodian-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure</t>
   </si>
 </sst>
 </file>
@@ -2008,7 +2011,9 @@
       <c r="K13" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>assignedCustodian, contient l’élément representedCustodianOrganization caractérisant la structure conservant le document.</t>
+    <t>L'élément de l'en-tête du CDA assignedCustodian contient l’élément representedCustodianOrganization caractérisant la structure conservant le document.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-custodian.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
